--- a/data/sample_offline.xlsx
+++ b/data/sample_offline.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,68 +413,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L237"/>
+  <dimension ref="A1:M237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>고객 참조 번호</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>판매처명</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>오더유형</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>대분류내역</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>제품명</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>S/O수량</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>S/O sum</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>포인트</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>배송비</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>쇼핑백</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>납품요청일자</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>오더사유명</t>
         </is>
       </c>
     </row>
@@ -537,6 +530,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,6 +575,7 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,6 +624,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -677,6 +673,7 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -725,6 +722,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -773,6 +771,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -821,6 +820,7 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -869,6 +869,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -917,6 +918,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -965,6 +967,7 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1013,6 +1016,7 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1061,6 +1065,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1109,6 +1114,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1157,6 +1163,11 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>반품-기타사유</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1205,6 +1216,7 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1253,6 +1265,7 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1301,6 +1314,11 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>반품-교환</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1349,6 +1367,7 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1397,6 +1416,11 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1445,6 +1469,7 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1493,6 +1518,7 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1541,6 +1567,7 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1589,6 +1616,11 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1637,6 +1669,7 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1685,6 +1718,7 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1733,6 +1767,7 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1781,6 +1816,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1829,6 +1865,7 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1877,6 +1914,7 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1925,6 +1963,7 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1973,6 +2012,7 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2021,6 +2061,7 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2069,6 +2110,7 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2117,6 +2159,7 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2165,6 +2208,11 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2209,6 +2257,11 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2257,6 +2310,7 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2305,6 +2359,11 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2353,6 +2412,7 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2401,6 +2461,7 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2449,6 +2510,11 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2497,6 +2563,7 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2545,6 +2612,7 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2593,6 +2661,7 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2641,6 +2710,7 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2689,6 +2759,7 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2737,6 +2808,11 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2785,6 +2861,7 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2833,6 +2910,7 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2877,6 +2955,11 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2925,6 +3008,7 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2973,6 +3057,7 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3021,6 +3106,7 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3069,6 +3155,7 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3117,6 +3204,11 @@
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3165,6 +3257,7 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3209,6 +3302,7 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3257,6 +3351,7 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3305,6 +3400,11 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>반품-교환</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3353,6 +3453,7 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3401,6 +3502,7 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3449,6 +3551,7 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3497,6 +3600,7 @@
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3545,6 +3649,7 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3593,6 +3698,7 @@
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3641,6 +3747,7 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3689,6 +3796,7 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3737,6 +3845,7 @@
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3785,6 +3894,7 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3833,6 +3943,7 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3881,6 +3992,11 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3929,6 +4045,7 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3977,6 +4094,7 @@
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4025,6 +4143,7 @@
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4073,6 +4192,7 @@
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4121,6 +4241,7 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4169,6 +4290,7 @@
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4217,6 +4339,7 @@
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4265,6 +4388,7 @@
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4357,6 +4482,7 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4405,6 +4531,7 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4449,6 +4576,11 @@
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4497,6 +4629,7 @@
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4545,6 +4678,7 @@
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4593,6 +4727,7 @@
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4641,6 +4776,7 @@
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4689,6 +4825,7 @@
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4737,6 +4874,11 @@
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4781,6 +4923,7 @@
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4829,6 +4972,7 @@
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4877,6 +5021,11 @@
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4925,6 +5074,7 @@
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4973,6 +5123,7 @@
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5021,6 +5172,7 @@
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5069,6 +5221,7 @@
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5117,6 +5270,7 @@
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5165,6 +5319,7 @@
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5213,6 +5368,7 @@
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5261,6 +5417,7 @@
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5309,6 +5466,7 @@
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5357,6 +5515,11 @@
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5405,6 +5568,7 @@
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5453,6 +5617,7 @@
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5501,6 +5666,7 @@
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5549,6 +5715,11 @@
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5597,6 +5768,7 @@
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5645,6 +5817,7 @@
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5693,6 +5866,7 @@
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5741,6 +5915,11 @@
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5789,6 +5968,7 @@
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5837,6 +6017,11 @@
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5885,6 +6070,11 @@
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5933,6 +6123,11 @@
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5981,6 +6176,7 @@
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6029,6 +6225,7 @@
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6073,6 +6270,7 @@
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6121,6 +6319,11 @@
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6169,6 +6372,7 @@
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6217,6 +6421,11 @@
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6265,6 +6474,7 @@
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6313,6 +6523,7 @@
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6361,6 +6572,7 @@
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6409,6 +6621,11 @@
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6457,6 +6674,7 @@
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6505,6 +6723,11 @@
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6553,6 +6776,7 @@
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6601,6 +6825,7 @@
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6649,6 +6874,7 @@
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6693,6 +6919,7 @@
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6737,6 +6964,7 @@
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6785,6 +7013,7 @@
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6833,6 +7062,7 @@
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6881,6 +7111,7 @@
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6929,6 +7160,7 @@
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6977,6 +7209,7 @@
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7025,6 +7258,7 @@
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7073,6 +7307,7 @@
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7121,6 +7356,7 @@
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7165,6 +7401,7 @@
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7213,6 +7450,11 @@
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7261,6 +7503,11 @@
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7309,6 +7556,7 @@
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7357,6 +7605,7 @@
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7405,6 +7654,7 @@
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7453,6 +7703,7 @@
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7501,6 +7752,7 @@
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7549,6 +7801,7 @@
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7597,6 +7850,11 @@
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7645,6 +7903,7 @@
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7693,6 +7952,7 @@
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7741,6 +8001,7 @@
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7789,6 +8050,7 @@
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7837,6 +8099,7 @@
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7885,6 +8148,7 @@
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7933,6 +8197,7 @@
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7977,6 +8242,11 @@
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8021,6 +8291,7 @@
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8069,6 +8340,7 @@
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8117,6 +8389,7 @@
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8161,6 +8434,11 @@
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8209,6 +8487,7 @@
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8257,6 +8536,7 @@
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8305,6 +8585,11 @@
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8353,6 +8638,11 @@
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8401,6 +8691,7 @@
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8449,6 +8740,7 @@
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8497,6 +8789,7 @@
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8545,6 +8838,7 @@
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8593,6 +8887,11 @@
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>반품-교환</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8641,6 +8940,7 @@
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8689,6 +8989,11 @@
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>반품-교환</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8737,6 +9042,11 @@
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8785,6 +9095,11 @@
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8833,6 +9148,7 @@
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8881,6 +9197,7 @@
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8929,6 +9246,7 @@
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8973,6 +9291,7 @@
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9021,6 +9340,7 @@
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9069,6 +9389,11 @@
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9113,6 +9438,7 @@
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9161,6 +9487,7 @@
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9209,6 +9536,7 @@
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9253,6 +9581,11 @@
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>반품-변심</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9301,6 +9634,7 @@
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9349,6 +9683,7 @@
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9397,6 +9732,7 @@
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9445,6 +9781,7 @@
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9493,6 +9830,7 @@
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9541,6 +9879,11 @@
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9585,6 +9928,7 @@
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9633,6 +9977,7 @@
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9677,6 +10022,7 @@
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9725,6 +10071,7 @@
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9773,6 +10120,11 @@
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9821,6 +10173,7 @@
         </is>
       </c>
       <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9869,6 +10222,7 @@
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9917,6 +10271,7 @@
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9965,6 +10320,7 @@
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10013,6 +10369,7 @@
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10061,6 +10418,7 @@
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10109,6 +10467,7 @@
         </is>
       </c>
       <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10157,6 +10516,11 @@
         </is>
       </c>
       <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10205,6 +10569,7 @@
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10253,6 +10618,7 @@
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10301,6 +10667,7 @@
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10349,6 +10716,7 @@
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10397,6 +10765,7 @@
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10441,6 +10810,7 @@
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10485,6 +10855,7 @@
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10533,6 +10904,7 @@
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10581,6 +10953,7 @@
         </is>
       </c>
       <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10629,6 +11002,7 @@
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10677,6 +11051,7 @@
         </is>
       </c>
       <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10721,6 +11096,7 @@
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10769,6 +11145,7 @@
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10817,6 +11194,7 @@
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10865,6 +11243,7 @@
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10913,6 +11292,7 @@
         </is>
       </c>
       <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10961,6 +11341,11 @@
         </is>
       </c>
       <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>빠른 반품</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -11009,6 +11394,7 @@
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -11057,6 +11443,7 @@
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11105,6 +11492,7 @@
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11149,6 +11537,7 @@
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11197,6 +11586,7 @@
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11245,6 +11635,7 @@
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11293,6 +11684,7 @@
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11341,6 +11733,7 @@
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11389,6 +11782,7 @@
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11433,6 +11827,7 @@
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11481,6 +11876,7 @@
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11529,6 +11925,7 @@
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11577,6 +11974,7 @@
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11625,6 +12023,11 @@
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>반품-교환</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11673,6 +12076,7 @@
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11721,6 +12125,7 @@
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
